--- a/day18/Day18-AI-Product-Finance-Model.xlsx
+++ b/day18/Day18-AI-Product-Finance-Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quang\Documents\AI20K26\track1\2A202600197_Nguyen-Quang-Tung_Track1\day18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF26EE1-C014-4B18-B9F5-B2FFF126DB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22910215-EA7F-4AB6-8486-21EF94907C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Assumptions" sheetId="1" r:id="rId1"/>
@@ -705,21 +705,6 @@
   </cellStyleXfs>
   <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -842,6 +827,21 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1288,107 +1288,107 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="8">
         <v>179000</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="8">
         <v>159000</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="8">
         <v>119000</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="15">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D8" s="15">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="E8" s="15">
-        <v>2E-3</v>
-      </c>
-      <c r="F8" s="14" t="s">
+      <c r="C8" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="8">
         <v>50000</v>
       </c>
-      <c r="D9" s="13">
-        <v>50000</v>
-      </c>
-      <c r="E9" s="13">
-        <v>50000</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="D9" s="8">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="8">
+        <v>60000</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H9" t="s">
@@ -1396,31 +1396,31 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="8">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E12" s="8">
         <v>30000</v>
       </c>
-      <c r="D12" s="13">
-        <v>50000</v>
-      </c>
-      <c r="E12" s="13">
-        <v>70000</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H12" t="s">
@@ -1428,22 +1428,22 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="8">
         <v>5000</v>
       </c>
-      <c r="D13" s="13">
-        <v>8000</v>
-      </c>
-      <c r="E13" s="13">
-        <v>12000</v>
-      </c>
-      <c r="F13" s="14" t="s">
+      <c r="D13" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="8">
+        <v>15000</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H13" t="s">
@@ -1451,325 +1451,325 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="13">
-        <v>3000</v>
-      </c>
-      <c r="D14" s="13">
-        <v>5000</v>
-      </c>
-      <c r="E14" s="13">
+      <c r="C14" s="8">
         <v>8000</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="D14" s="8">
+        <v>15000</v>
+      </c>
+      <c r="E14" s="8">
+        <v>15000</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="12">
         <f>C12+C13+C14</f>
-        <v>38000</v>
-      </c>
-      <c r="D15" s="17">
+        <v>33000</v>
+      </c>
+      <c r="D15" s="12">
         <f>D12+D13+D14</f>
-        <v>63000</v>
-      </c>
-      <c r="E15" s="17">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="12">
         <f>E12+E13+E14</f>
-        <v>90000</v>
-      </c>
-      <c r="F15" s="18"/>
+        <v>60000</v>
+      </c>
+      <c r="F15" s="13"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="10">
         <v>0.03</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="10">
         <v>0.05</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="10">
         <v>0.08</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="15">
         <f>IFERROR(1/C18,0)</f>
         <v>33.333333333333336</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="15">
         <f>IFERROR(1/D18,0)</f>
         <v>20</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="15">
         <f>IFERROR(1/E18,0)</f>
         <v>12.5</v>
       </c>
-      <c r="F19" s="21"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="8">
         <v>100000</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="8">
         <v>180000</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="8">
         <v>300000</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="8">
         <v>60000000</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="8">
         <v>90000000</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="8">
         <v>120000000</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="8">
         <v>8000000</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="8">
         <v>10000000</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="8">
         <v>15000000</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="8">
         <v>40000000</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="8">
         <v>25000000</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="8">
         <v>15000000</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="17">
         <f>SUM(C25:C27)</f>
         <v>108000000</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="17">
         <f>SUM(D25:D27)</f>
         <v>125000000</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="17">
         <f>SUM(E25:E27)</f>
         <v>150000000</v>
       </c>
-      <c r="F28" s="21"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="2:7" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="8">
         <v>10000000</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="8">
         <v>20000000</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="8">
         <v>30000000</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="8">
         <v>150000000</v>
       </c>
-      <c r="D32" s="13">
-        <v>300000000</v>
-      </c>
-      <c r="E32" s="13">
+      <c r="D32" s="8">
+        <v>350000000</v>
+      </c>
+      <c r="E32" s="8">
         <v>450000000</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
     </row>
     <row r="35" spans="2:7" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="10">
         <v>0.2</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="10">
         <v>0.2</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="10">
         <v>0.2</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="18">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="18">
         <f>(1+D35)^(1/12)-1</f>
         <v>1.5309470499731193E-2</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="18">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F36" s="21"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
     </row>
     <row r="39" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
     </row>
     <row r="40" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="41" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1803,287 +1803,287 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="19">
         <f>'1. Assumptions'!C7</f>
         <v>179000</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="19">
         <f>'1. Assumptions'!D7</f>
         <v>159000</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="19">
         <f>'1. Assumptions'!E7</f>
         <v>119000</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="19">
         <f>'1. Assumptions'!C15</f>
-        <v>38000</v>
-      </c>
-      <c r="D9" s="24">
+        <v>33000</v>
+      </c>
+      <c r="D9" s="19">
         <f>'1. Assumptions'!D15</f>
-        <v>63000</v>
-      </c>
-      <c r="E9" s="24">
+        <v>50000</v>
+      </c>
+      <c r="E9" s="19">
         <f>'1. Assumptions'!E15</f>
-        <v>90000</v>
-      </c>
-      <c r="F9" s="14" t="s">
+        <v>60000</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="17">
         <f>C8-C9</f>
-        <v>141000</v>
-      </c>
-      <c r="D10" s="22">
+        <v>146000</v>
+      </c>
+      <c r="D10" s="17">
         <f>D8-D9</f>
-        <v>96000</v>
-      </c>
-      <c r="E10" s="22">
+        <v>109000</v>
+      </c>
+      <c r="E10" s="17">
         <f>E8-E9</f>
-        <v>29000</v>
-      </c>
-      <c r="F10" s="21"/>
+        <v>59000</v>
+      </c>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="18">
         <f>IFERROR(C10/C8,0)</f>
-        <v>0.78770949720670391</v>
-      </c>
-      <c r="D11" s="23">
+        <v>0.81564245810055869</v>
+      </c>
+      <c r="D11" s="18">
         <f>IFERROR(D10/D8,0)</f>
-        <v>0.60377358490566035</v>
-      </c>
-      <c r="E11" s="23">
+        <v>0.68553459119496851</v>
+      </c>
+      <c r="E11" s="18">
         <f>IFERROR(E10/E8,0)</f>
-        <v>0.24369747899159663</v>
-      </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="6" t="s">
+        <v>0.49579831932773111</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="20">
         <f>'1. Assumptions'!C19</f>
         <v>33.333333333333336</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="20">
         <f>'1. Assumptions'!D19</f>
         <v>20</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="20">
         <f>'1. Assumptions'!E19</f>
         <v>12.5</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="17">
         <f>C10*C14</f>
-        <v>4700000</v>
-      </c>
-      <c r="D15" s="22">
+        <v>4866666.666666667</v>
+      </c>
+      <c r="D15" s="17">
         <f>D10*D14</f>
-        <v>1920000</v>
-      </c>
-      <c r="E15" s="22">
+        <v>2180000</v>
+      </c>
+      <c r="E15" s="17">
         <f>E10*E14</f>
-        <v>362500</v>
-      </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="6" t="s">
+        <v>737500</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="19">
         <f>'1. Assumptions'!C22</f>
         <v>100000</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="19">
         <f>'1. Assumptions'!D22</f>
         <v>180000</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="19">
         <f>'1. Assumptions'!E22</f>
         <v>300000</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="21">
         <f>IFERROR(C15/C18,0)</f>
-        <v>47</v>
-      </c>
-      <c r="D21" s="26">
+        <v>48.666666666666671</v>
+      </c>
+      <c r="D21" s="21">
         <f>IFERROR(D15/D18,0)</f>
-        <v>10.666666666666666</v>
-      </c>
-      <c r="E21" s="26">
+        <v>12.111111111111111</v>
+      </c>
+      <c r="E21" s="21">
         <f>IFERROR(E15/E18,0)</f>
-        <v>1.2083333333333333</v>
-      </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="6" t="s">
+        <v>2.4583333333333335</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="15">
         <f>IFERROR(C18/C10,0)</f>
-        <v>0.70921985815602839</v>
-      </c>
-      <c r="D22" s="20">
+        <v>0.68493150684931503</v>
+      </c>
+      <c r="D22" s="15">
         <f>IFERROR(D18/D10,0)</f>
-        <v>1.875</v>
-      </c>
-      <c r="E22" s="20">
+        <v>1.6513761467889909</v>
+      </c>
+      <c r="E22" s="15">
         <f>IFERROR(E18/E10,0)</f>
-        <v>10.344827586206897</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="6" t="s">
+        <v>5.0847457627118642</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="27" t="str">
+      <c r="C25" s="22" t="str">
         <f>IF(AND(C21&gt;=3,C22&lt;=12),"✓ HEALTHY",IF(OR(C21&lt;1,C22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>✓ HEALTHY</v>
       </c>
-      <c r="D25" s="27" t="str">
+      <c r="D25" s="22" t="str">
         <f>IF(AND(D21&gt;=3,D22&lt;=12),"✓ HEALTHY",IF(OR(D21&lt;1,D22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>✓ HEALTHY</v>
       </c>
-      <c r="E25" s="27" t="str">
+      <c r="E25" s="22" t="str">
         <f>IF(AND(E21&gt;=3,E22&lt;=12),"✓ HEALTHY",IF(OR(E21&lt;1,E22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v>⚠ WATCH</v>
       </c>
@@ -2139,1481 +2139,1481 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <f>MATCH(C4,{"Optimistic","Base","Pessimistic"},0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="26" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C7,'1. Assumptions'!D7,'1. Assumptions'!E7)</f>
-        <v>159000</v>
+        <v>179000</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C8,'1. Assumptions'!D8,'1. Assumptions'!E8)</f>
-        <v>6.0000000000000001E-3</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C9,'1. Assumptions'!D9,'1. Assumptions'!E9)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C15,'1. Assumptions'!D15,'1. Assumptions'!E15)</f>
-        <v>63000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C18,'1. Assumptions'!D18,'1. Assumptions'!E18)</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C22,'1. Assumptions'!D22,'1. Assumptions'!E22)</f>
-        <v>180000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C28,'1. Assumptions'!D28,'1. Assumptions'!E28)</f>
-        <v>125000000</v>
+        <v>108000000</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C31,'1. Assumptions'!D31,'1. Assumptions'!E31)</f>
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="28">
         <f>CHOOSE($C$6,'1. Assumptions'!C32,'1. Assumptions'!D32,'1. Assumptions'!E32)</f>
-        <v>300000000</v>
+        <v>150000000</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="29">
         <f>CHOOSE($C$6,'1. Assumptions'!C36,'1. Assumptions'!D36,'1. Assumptions'!E36)</f>
-        <v>1.5309470499731193E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
+      <c r="W20" s="51"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="51"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="51"/>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="H21" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="K21" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="L21" s="36" t="s">
+      <c r="L21" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="N21" s="36" t="s">
+      <c r="N21" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="O21" s="36" t="s">
+      <c r="O21" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="P21" s="36" t="s">
+      <c r="P21" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="Q21" s="36" t="s">
+      <c r="Q21" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="R21" s="36" t="s">
+      <c r="R21" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="S21" s="36" t="s">
+      <c r="S21" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="T21" s="36" t="s">
+      <c r="T21" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="U21" s="36" t="s">
+      <c r="U21" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="V21" s="36" t="s">
+      <c r="V21" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="W21" s="36" t="s">
+      <c r="W21" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="X21" s="36" t="s">
+      <c r="X21" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="Y21" s="36" t="s">
+      <c r="Y21" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="Z21" s="36" t="s">
+      <c r="Z21" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="AA21" s="37" t="s">
+      <c r="AA21" s="32" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="33">
         <f t="shared" ref="C22:Z22" si="0">ROUND($C$10*$C$9,0)</f>
-        <v>300</v>
-      </c>
-      <c r="D22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="D22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="E22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="F22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="F22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="G22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="G22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="H22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="H22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="I22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="I22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="J22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="J22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="K22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="K22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="L22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="L22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="M22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="M22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="N22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="N22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="O22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="O22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="P22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="P22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="Q22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="Q22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="R22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="R22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="S22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="S22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="T22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="T22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="U22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="U22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="V22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="W22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="W22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="X22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="X22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="Y22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="Y22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="Z22" s="38">
+        <v>2500</v>
+      </c>
+      <c r="Z22" s="33">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="AA22" s="39">
+        <v>2500</v>
+      </c>
+      <c r="AA22" s="34">
         <f>SUM(C22:Z22)</f>
-        <v>7200</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="33">
         <f>C22</f>
-        <v>300</v>
-      </c>
-      <c r="D23" s="38">
+        <v>2500</v>
+      </c>
+      <c r="D23" s="33">
         <f t="shared" ref="D23:Z23" si="1">C23*(1-$C$12)+D22</f>
-        <v>585</v>
-      </c>
-      <c r="E23" s="38">
+        <v>4925</v>
+      </c>
+      <c r="E23" s="33">
         <f t="shared" si="1"/>
-        <v>855.75</v>
-      </c>
-      <c r="F23" s="38">
+        <v>7277.25</v>
+      </c>
+      <c r="F23" s="33">
         <f t="shared" si="1"/>
-        <v>1112.9625000000001</v>
-      </c>
-      <c r="G23" s="38">
+        <v>9558.932499999999</v>
+      </c>
+      <c r="G23" s="33">
         <f t="shared" si="1"/>
-        <v>1357.3143749999999</v>
-      </c>
-      <c r="H23" s="38">
+        <v>11772.164524999998</v>
+      </c>
+      <c r="H23" s="33">
         <f t="shared" si="1"/>
-        <v>1589.4486562499999</v>
-      </c>
-      <c r="I23" s="38">
+        <v>13918.999589249997</v>
+      </c>
+      <c r="I23" s="33">
         <f t="shared" si="1"/>
-        <v>1809.9762234374998</v>
-      </c>
-      <c r="J23" s="38">
+        <v>16001.429601572498</v>
+      </c>
+      <c r="J23" s="33">
         <f t="shared" si="1"/>
-        <v>2019.4774122656247</v>
-      </c>
-      <c r="K23" s="38">
+        <v>18021.386713525324</v>
+      </c>
+      <c r="K23" s="33">
         <f t="shared" si="1"/>
-        <v>2218.5035416523433</v>
-      </c>
-      <c r="L23" s="38">
+        <v>19980.745112119563</v>
+      </c>
+      <c r="L23" s="33">
         <f t="shared" si="1"/>
-        <v>2407.5783645697261</v>
-      </c>
-      <c r="M23" s="38">
+        <v>21881.322758755974</v>
+      </c>
+      <c r="M23" s="33">
         <f t="shared" si="1"/>
-        <v>2587.1994463412398</v>
-      </c>
-      <c r="N23" s="38">
+        <v>23724.883075993293</v>
+      </c>
+      <c r="N23" s="33">
         <f t="shared" si="1"/>
-        <v>2757.8394740241774</v>
-      </c>
-      <c r="O23" s="38">
+        <v>25513.136583713494</v>
+      </c>
+      <c r="O23" s="33">
         <f t="shared" si="1"/>
-        <v>2919.9475003229686</v>
-      </c>
-      <c r="P23" s="38">
+        <v>27247.742486202089</v>
+      </c>
+      <c r="P23" s="33">
         <f t="shared" si="1"/>
-        <v>3073.9501253068202</v>
-      </c>
-      <c r="Q23" s="38">
+        <v>28930.310211616026</v>
+      </c>
+      <c r="Q23" s="33">
         <f t="shared" si="1"/>
-        <v>3220.2526190414792</v>
-      </c>
-      <c r="R23" s="38">
+        <v>30562.400905267543</v>
+      </c>
+      <c r="R23" s="33">
         <f t="shared" si="1"/>
-        <v>3359.239988089405</v>
-      </c>
-      <c r="S23" s="38">
+        <v>32145.528878109515</v>
+      </c>
+      <c r="S23" s="33">
         <f t="shared" si="1"/>
-        <v>3491.2779886849344</v>
-      </c>
-      <c r="T23" s="38">
+        <v>33681.163011766228</v>
+      </c>
+      <c r="T23" s="33">
         <f t="shared" si="1"/>
-        <v>3616.7140892506877</v>
-      </c>
-      <c r="U23" s="38">
+        <v>35170.728121413238</v>
+      </c>
+      <c r="U23" s="33">
         <f t="shared" si="1"/>
-        <v>3735.8783847881532</v>
-      </c>
-      <c r="V23" s="38">
+        <v>36615.606277770843</v>
+      </c>
+      <c r="V23" s="33">
         <f t="shared" si="1"/>
-        <v>3849.0844655487454</v>
-      </c>
-      <c r="W23" s="38">
+        <v>38017.138089437714</v>
+      </c>
+      <c r="W23" s="33">
         <f t="shared" si="1"/>
-        <v>3956.6302422713079</v>
-      </c>
-      <c r="X23" s="38">
+        <v>39376.623946754582</v>
+      </c>
+      <c r="X23" s="33">
         <f t="shared" si="1"/>
-        <v>4058.7987301577423</v>
-      </c>
-      <c r="Y23" s="38">
+        <v>40695.325228351947</v>
+      </c>
+      <c r="Y23" s="33">
         <f t="shared" si="1"/>
-        <v>4155.8587936498552</v>
-      </c>
-      <c r="Z23" s="38">
+        <v>41974.465471501389</v>
+      </c>
+      <c r="Z23" s="33">
         <f t="shared" si="1"/>
-        <v>4248.0658539673623</v>
+        <v>43215.231507356344</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="36">
         <f t="shared" ref="C25:Z25" si="2">C23*$C$8</f>
-        <v>47700000</v>
-      </c>
-      <c r="D25" s="41">
+        <v>447500000</v>
+      </c>
+      <c r="D25" s="36">
         <f t="shared" si="2"/>
-        <v>93015000</v>
-      </c>
-      <c r="E25" s="41">
+        <v>881575000</v>
+      </c>
+      <c r="E25" s="36">
         <f t="shared" si="2"/>
-        <v>136064250</v>
-      </c>
-      <c r="F25" s="41">
+        <v>1302627750</v>
+      </c>
+      <c r="F25" s="36">
         <f t="shared" si="2"/>
-        <v>176961037.5</v>
-      </c>
-      <c r="G25" s="41">
+        <v>1711048917.4999998</v>
+      </c>
+      <c r="G25" s="36">
         <f t="shared" si="2"/>
-        <v>215812985.625</v>
-      </c>
-      <c r="H25" s="41">
+        <v>2107217449.9749997</v>
+      </c>
+      <c r="H25" s="36">
         <f t="shared" si="2"/>
-        <v>252722336.34374997</v>
-      </c>
-      <c r="I25" s="41">
+        <v>2491500926.4757495</v>
+      </c>
+      <c r="I25" s="36">
         <f t="shared" si="2"/>
-        <v>287786219.52656245</v>
-      </c>
-      <c r="J25" s="41">
+        <v>2864255898.6814771</v>
+      </c>
+      <c r="J25" s="36">
         <f t="shared" si="2"/>
-        <v>321096908.55023432</v>
-      </c>
-      <c r="K25" s="41">
+        <v>3225828221.7210331</v>
+      </c>
+      <c r="K25" s="36">
         <f t="shared" si="2"/>
-        <v>352742063.12272257</v>
-      </c>
-      <c r="L25" s="41">
+        <v>3576553375.0694017</v>
+      </c>
+      <c r="L25" s="36">
         <f t="shared" si="2"/>
-        <v>382804959.96658647</v>
-      </c>
-      <c r="M25" s="41">
+        <v>3916756773.8173194</v>
+      </c>
+      <c r="M25" s="36">
         <f t="shared" si="2"/>
-        <v>411364711.96825713</v>
-      </c>
-      <c r="N25" s="41">
+        <v>4246754070.6027994</v>
+      </c>
+      <c r="N25" s="36">
         <f t="shared" si="2"/>
-        <v>438496476.3698442</v>
-      </c>
-      <c r="O25" s="41">
+        <v>4566851448.4847155</v>
+      </c>
+      <c r="O25" s="36">
         <f t="shared" si="2"/>
-        <v>464271652.55135202</v>
-      </c>
-      <c r="P25" s="41">
+        <v>4877345905.0301743</v>
+      </c>
+      <c r="P25" s="36">
         <f t="shared" si="2"/>
-        <v>488758069.92378438</v>
-      </c>
-      <c r="Q25" s="41">
+        <v>5178525527.8792686</v>
+      </c>
+      <c r="Q25" s="36">
         <f t="shared" si="2"/>
-        <v>512020166.4275952</v>
-      </c>
-      <c r="R25" s="41">
+        <v>5470669762.0428905</v>
+      </c>
+      <c r="R25" s="36">
         <f t="shared" si="2"/>
-        <v>534119158.10621542</v>
-      </c>
-      <c r="S25" s="41">
+        <v>5754049669.1816034</v>
+      </c>
+      <c r="S25" s="36">
         <f t="shared" si="2"/>
-        <v>555113200.20090461</v>
-      </c>
-      <c r="T25" s="41">
+        <v>6028928179.1061544</v>
+      </c>
+      <c r="T25" s="36">
         <f t="shared" si="2"/>
-        <v>575057540.19085932</v>
-      </c>
-      <c r="U25" s="41">
+        <v>6295560333.7329693</v>
+      </c>
+      <c r="U25" s="36">
         <f t="shared" si="2"/>
-        <v>594004663.18131638</v>
-      </c>
-      <c r="V25" s="41">
+        <v>6554193523.7209806</v>
+      </c>
+      <c r="V25" s="36">
         <f t="shared" si="2"/>
-        <v>612004430.02225053</v>
-      </c>
-      <c r="W25" s="41">
+        <v>6805067718.0093508</v>
+      </c>
+      <c r="W25" s="36">
         <f t="shared" si="2"/>
-        <v>629104208.52113795</v>
-      </c>
-      <c r="X25" s="41">
+        <v>7048415686.4690704</v>
+      </c>
+      <c r="X25" s="36">
         <f t="shared" si="2"/>
-        <v>645348998.09508097</v>
-      </c>
-      <c r="Y25" s="41">
+        <v>7284463215.8749981</v>
+      </c>
+      <c r="Y25" s="36">
         <f t="shared" si="2"/>
-        <v>660781548.19032693</v>
-      </c>
-      <c r="Z25" s="41">
+        <v>7513429319.3987484</v>
+      </c>
+      <c r="Z25" s="36">
         <f t="shared" si="2"/>
-        <v>675442470.78081059</v>
-      </c>
-      <c r="AA25" s="42">
+        <v>7735526439.8167858</v>
+      </c>
+      <c r="AA25" s="37">
         <f t="shared" ref="AA25:AA30" si="3">SUM(C25:Z25)</f>
-        <v>10062593055.164593</v>
+        <v>107884645112.5905</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="38">
+      <c r="C26" s="33">
         <f t="shared" ref="C26:Z26" si="4">C23*$C$11</f>
-        <v>18900000</v>
-      </c>
-      <c r="D26" s="38">
+        <v>82500000</v>
+      </c>
+      <c r="D26" s="33">
         <f t="shared" si="4"/>
-        <v>36855000</v>
-      </c>
-      <c r="E26" s="38">
+        <v>162525000</v>
+      </c>
+      <c r="E26" s="33">
         <f t="shared" si="4"/>
-        <v>53912250</v>
-      </c>
-      <c r="F26" s="38">
+        <v>240149250</v>
+      </c>
+      <c r="F26" s="33">
         <f t="shared" si="4"/>
-        <v>70116637.5</v>
-      </c>
-      <c r="G26" s="38">
+        <v>315444772.49999994</v>
+      </c>
+      <c r="G26" s="33">
         <f t="shared" si="4"/>
-        <v>85510805.625</v>
-      </c>
-      <c r="H26" s="38">
+        <v>388481429.32499993</v>
+      </c>
+      <c r="H26" s="33">
         <f t="shared" si="4"/>
-        <v>100135265.34375</v>
-      </c>
-      <c r="I26" s="38">
+        <v>459326986.44524992</v>
+      </c>
+      <c r="I26" s="33">
         <f t="shared" si="4"/>
-        <v>114028502.07656249</v>
-      </c>
-      <c r="J26" s="38">
+        <v>528047176.85189241</v>
+      </c>
+      <c r="J26" s="33">
         <f t="shared" si="4"/>
-        <v>127227076.97273436</v>
-      </c>
-      <c r="K26" s="38">
+        <v>594705761.5463357</v>
+      </c>
+      <c r="K26" s="33">
         <f t="shared" si="4"/>
-        <v>139765723.12409762</v>
-      </c>
-      <c r="L26" s="38">
+        <v>659364588.69994557</v>
+      </c>
+      <c r="L26" s="33">
         <f t="shared" si="4"/>
-        <v>151677436.96789274</v>
-      </c>
-      <c r="M26" s="38">
+        <v>722083651.03894711</v>
+      </c>
+      <c r="M26" s="33">
         <f t="shared" si="4"/>
-        <v>162993565.1194981</v>
-      </c>
-      <c r="N26" s="38">
+        <v>782921141.50777864</v>
+      </c>
+      <c r="N26" s="33">
         <f t="shared" si="4"/>
-        <v>173743886.86352319</v>
-      </c>
-      <c r="O26" s="38">
+        <v>841933507.26254535</v>
+      </c>
+      <c r="O26" s="33">
         <f t="shared" si="4"/>
-        <v>183956692.52034703</v>
-      </c>
-      <c r="P26" s="38">
+        <v>899175502.04466891</v>
+      </c>
+      <c r="P26" s="33">
         <f t="shared" si="4"/>
-        <v>193658857.89432967</v>
-      </c>
-      <c r="Q26" s="38">
+        <v>954700236.98332882</v>
+      </c>
+      <c r="Q26" s="33">
         <f t="shared" si="4"/>
-        <v>202875914.9996132</v>
-      </c>
-      <c r="R26" s="38">
+        <v>1008559229.8738289</v>
+      </c>
+      <c r="R26" s="33">
         <f t="shared" si="4"/>
-        <v>211632119.24963251</v>
-      </c>
-      <c r="S26" s="38">
+        <v>1060802452.977614</v>
+      </c>
+      <c r="S26" s="33">
         <f t="shared" si="4"/>
-        <v>219950513.28715086</v>
-      </c>
-      <c r="T26" s="38">
+        <v>1111478379.3882856</v>
+      </c>
+      <c r="T26" s="33">
         <f t="shared" si="4"/>
-        <v>227852987.62279332</v>
-      </c>
-      <c r="U26" s="38">
+        <v>1160634028.0066369</v>
+      </c>
+      <c r="U26" s="33">
         <f t="shared" si="4"/>
-        <v>235360338.24165365</v>
-      </c>
-      <c r="V26" s="38">
+        <v>1208315007.1664379</v>
+      </c>
+      <c r="V26" s="33">
         <f t="shared" si="4"/>
-        <v>242492321.32957095</v>
-      </c>
-      <c r="W26" s="38">
+        <v>1254565556.9514446</v>
+      </c>
+      <c r="W26" s="33">
         <f t="shared" si="4"/>
-        <v>249267705.2630924</v>
-      </c>
-      <c r="X26" s="38">
+        <v>1299428590.2429011</v>
+      </c>
+      <c r="X26" s="33">
         <f t="shared" si="4"/>
-        <v>255704319.99993777</v>
-      </c>
-      <c r="Y26" s="38">
+        <v>1342945732.5356143</v>
+      </c>
+      <c r="Y26" s="33">
         <f t="shared" si="4"/>
-        <v>261819103.99994087</v>
-      </c>
-      <c r="Z26" s="38">
+        <v>1385157360.5595458</v>
+      </c>
+      <c r="Z26" s="33">
         <f t="shared" si="4"/>
-        <v>267628148.79994383</v>
-      </c>
-      <c r="AA26" s="39">
+        <v>1426102639.7427595</v>
+      </c>
+      <c r="AA26" s="34">
         <f t="shared" si="3"/>
-        <v>3987065172.8010645</v>
+        <v>19889347981.650761</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="38">
         <f t="shared" ref="C27:Z27" si="5">C25-C26</f>
-        <v>28800000</v>
-      </c>
-      <c r="D27" s="43">
+        <v>365000000</v>
+      </c>
+      <c r="D27" s="38">
         <f t="shared" si="5"/>
-        <v>56160000</v>
-      </c>
-      <c r="E27" s="43">
+        <v>719050000</v>
+      </c>
+      <c r="E27" s="38">
         <f t="shared" si="5"/>
-        <v>82152000</v>
-      </c>
-      <c r="F27" s="43">
+        <v>1062478500</v>
+      </c>
+      <c r="F27" s="38">
         <f t="shared" si="5"/>
-        <v>106844400</v>
-      </c>
-      <c r="G27" s="43">
+        <v>1395604144.9999998</v>
+      </c>
+      <c r="G27" s="38">
         <f t="shared" si="5"/>
-        <v>130302180</v>
-      </c>
-      <c r="H27" s="43">
+        <v>1718736020.6499996</v>
+      </c>
+      <c r="H27" s="38">
         <f t="shared" si="5"/>
-        <v>152587070.99999997</v>
-      </c>
-      <c r="I27" s="43">
+        <v>2032173940.0304995</v>
+      </c>
+      <c r="I27" s="38">
         <f t="shared" si="5"/>
-        <v>173757717.44999996</v>
-      </c>
-      <c r="J27" s="43">
+        <v>2336208721.8295846</v>
+      </c>
+      <c r="J27" s="38">
         <f t="shared" si="5"/>
-        <v>193869831.57749996</v>
-      </c>
-      <c r="K27" s="43">
+        <v>2631122460.1746974</v>
+      </c>
+      <c r="K27" s="38">
         <f t="shared" si="5"/>
-        <v>212976339.99862495</v>
-      </c>
-      <c r="L27" s="43">
+        <v>2917188786.3694563</v>
+      </c>
+      <c r="L27" s="38">
         <f t="shared" si="5"/>
-        <v>231127522.99869373</v>
-      </c>
-      <c r="M27" s="43">
+        <v>3194673122.7783723</v>
+      </c>
+      <c r="M27" s="38">
         <f t="shared" si="5"/>
-        <v>248371146.84875903</v>
-      </c>
-      <c r="N27" s="43">
+        <v>3463832929.0950208</v>
+      </c>
+      <c r="N27" s="38">
         <f t="shared" si="5"/>
-        <v>264752589.50632101</v>
-      </c>
-      <c r="O27" s="43">
+        <v>3724917941.2221699</v>
+      </c>
+      <c r="O27" s="38">
         <f t="shared" si="5"/>
-        <v>280314960.03100502</v>
-      </c>
-      <c r="P27" s="43">
+        <v>3978170402.9855051</v>
+      </c>
+      <c r="P27" s="38">
         <f t="shared" si="5"/>
-        <v>295099212.02945471</v>
-      </c>
-      <c r="Q27" s="43">
+        <v>4223825290.8959398</v>
+      </c>
+      <c r="Q27" s="38">
         <f t="shared" si="5"/>
-        <v>309144251.42798197</v>
-      </c>
-      <c r="R27" s="43">
+        <v>4462110532.1690617</v>
+      </c>
+      <c r="R27" s="38">
         <f t="shared" si="5"/>
-        <v>322487038.85658288</v>
-      </c>
-      <c r="S27" s="43">
+        <v>4693247216.203989</v>
+      </c>
+      <c r="S27" s="38">
         <f t="shared" si="5"/>
-        <v>335162686.91375375</v>
-      </c>
-      <c r="T27" s="43">
+        <v>4917449799.7178688</v>
+      </c>
+      <c r="T27" s="38">
         <f t="shared" si="5"/>
-        <v>347204552.568066</v>
-      </c>
-      <c r="U27" s="43">
+        <v>5134926305.7263327</v>
+      </c>
+      <c r="U27" s="38">
         <f t="shared" si="5"/>
-        <v>358644324.93966269</v>
-      </c>
-      <c r="V27" s="43">
+        <v>5345878516.5545425</v>
+      </c>
+      <c r="V27" s="38">
         <f t="shared" si="5"/>
-        <v>369512108.69267958</v>
-      </c>
-      <c r="W27" s="43">
+        <v>5550502161.0579062</v>
+      </c>
+      <c r="W27" s="38">
         <f t="shared" si="5"/>
-        <v>379836503.25804555</v>
-      </c>
-      <c r="X27" s="43">
+        <v>5748987096.2261696</v>
+      </c>
+      <c r="X27" s="38">
         <f t="shared" si="5"/>
-        <v>389644678.0951432</v>
-      </c>
-      <c r="Y27" s="43">
+        <v>5941517483.3393841</v>
+      </c>
+      <c r="Y27" s="38">
         <f t="shared" si="5"/>
-        <v>398962444.19038606</v>
-      </c>
-      <c r="Z27" s="43">
+        <v>6128271958.8392029</v>
+      </c>
+      <c r="Z27" s="38">
         <f t="shared" si="5"/>
-        <v>407814321.98086679</v>
-      </c>
-      <c r="AA27" s="39">
+        <v>6309423800.0740261</v>
+      </c>
+      <c r="AA27" s="34">
         <f t="shared" si="3"/>
-        <v>6075527882.3635254</v>
+        <v>87995297130.939728</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="33">
         <f t="shared" ref="C28:Z28" si="6">C22*$C$13</f>
-        <v>54000000</v>
-      </c>
-      <c r="D28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="D28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="E28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="E28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="F28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="F28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="G28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="G28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="H28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="H28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="I28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="I28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="J28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="J28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="K28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="K28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="L28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="L28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="M28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="M28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="N28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="N28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="O28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="O28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="P28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="P28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="Q28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="Q28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="R28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="R28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="S28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="S28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="T28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="T28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="U28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="U28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="V28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="V28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="W28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="W28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="X28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="X28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="Y28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="Y28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="Z28" s="38">
+        <v>250000000</v>
+      </c>
+      <c r="Z28" s="33">
         <f t="shared" si="6"/>
-        <v>54000000</v>
-      </c>
-      <c r="AA28" s="39">
+        <v>250000000</v>
+      </c>
+      <c r="AA28" s="34">
         <f t="shared" si="3"/>
-        <v>1296000000</v>
+        <v>6000000000</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="33">
         <f t="shared" ref="C29:Z29" si="7">$C$14</f>
-        <v>125000000</v>
-      </c>
-      <c r="D29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="D29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="E29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="E29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="F29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="F29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="G29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="G29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="H29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="H29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="I29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="I29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="J29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="J29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="K29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="K29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="L29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="L29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="M29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="M29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="N29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="N29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="O29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="O29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="P29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="P29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="Q29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="Q29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="R29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="R29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="S29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="S29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="T29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="T29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="U29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="U29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="V29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="V29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="W29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="W29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="X29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="X29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="Y29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="Y29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="Z29" s="38">
+        <v>108000000</v>
+      </c>
+      <c r="Z29" s="33">
         <f t="shared" si="7"/>
-        <v>125000000</v>
-      </c>
-      <c r="AA29" s="39">
+        <v>108000000</v>
+      </c>
+      <c r="AA29" s="34">
         <f t="shared" si="3"/>
-        <v>3000000000</v>
+        <v>2592000000</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="39">
         <f t="shared" ref="C30:Z30" si="8">C27-C28-C29</f>
-        <v>-150200000</v>
-      </c>
-      <c r="D30" s="44">
+        <v>7000000</v>
+      </c>
+      <c r="D30" s="39">
         <f t="shared" si="8"/>
-        <v>-122840000</v>
-      </c>
-      <c r="E30" s="44">
+        <v>361050000</v>
+      </c>
+      <c r="E30" s="39">
         <f t="shared" si="8"/>
-        <v>-96848000</v>
-      </c>
-      <c r="F30" s="44">
+        <v>704478500</v>
+      </c>
+      <c r="F30" s="39">
         <f t="shared" si="8"/>
-        <v>-72155600</v>
-      </c>
-      <c r="G30" s="44">
+        <v>1037604144.9999998</v>
+      </c>
+      <c r="G30" s="39">
         <f t="shared" si="8"/>
-        <v>-48697820</v>
-      </c>
-      <c r="H30" s="44">
+        <v>1360736020.6499996</v>
+      </c>
+      <c r="H30" s="39">
         <f t="shared" si="8"/>
-        <v>-26412929.00000003</v>
-      </c>
-      <c r="I30" s="44">
+        <v>1674173940.0304995</v>
+      </c>
+      <c r="I30" s="39">
         <f t="shared" si="8"/>
-        <v>-5242282.5500000417</v>
-      </c>
-      <c r="J30" s="44">
+        <v>1978208721.8295846</v>
+      </c>
+      <c r="J30" s="39">
         <f t="shared" si="8"/>
-        <v>14869831.577499956</v>
-      </c>
-      <c r="K30" s="44">
+        <v>2273122460.1746974</v>
+      </c>
+      <c r="K30" s="39">
         <f t="shared" si="8"/>
-        <v>33976339.998624951</v>
-      </c>
-      <c r="L30" s="44">
+        <v>2559188786.3694563</v>
+      </c>
+      <c r="L30" s="39">
         <f t="shared" si="8"/>
-        <v>52127522.998693734</v>
-      </c>
-      <c r="M30" s="44">
+        <v>2836673122.7783723</v>
+      </c>
+      <c r="M30" s="39">
         <f t="shared" si="8"/>
-        <v>69371146.848759025</v>
-      </c>
-      <c r="N30" s="44">
+        <v>3105832929.0950208</v>
+      </c>
+      <c r="N30" s="39">
         <f t="shared" si="8"/>
-        <v>85752589.506321013</v>
-      </c>
-      <c r="O30" s="44">
+        <v>3366917941.2221699</v>
+      </c>
+      <c r="O30" s="39">
         <f t="shared" si="8"/>
-        <v>101314960.03100502</v>
-      </c>
-      <c r="P30" s="44">
+        <v>3620170402.9855051</v>
+      </c>
+      <c r="P30" s="39">
         <f t="shared" si="8"/>
-        <v>116099212.02945471</v>
-      </c>
-      <c r="Q30" s="44">
+        <v>3865825290.8959398</v>
+      </c>
+      <c r="Q30" s="39">
         <f t="shared" si="8"/>
-        <v>130144251.42798197</v>
-      </c>
-      <c r="R30" s="44">
+        <v>4104110532.1690617</v>
+      </c>
+      <c r="R30" s="39">
         <f t="shared" si="8"/>
-        <v>143487038.85658288</v>
-      </c>
-      <c r="S30" s="44">
+        <v>4335247216.203989</v>
+      </c>
+      <c r="S30" s="39">
         <f t="shared" si="8"/>
-        <v>156162686.91375375</v>
-      </c>
-      <c r="T30" s="44">
+        <v>4559449799.7178688</v>
+      </c>
+      <c r="T30" s="39">
         <f t="shared" si="8"/>
-        <v>168204552.568066</v>
-      </c>
-      <c r="U30" s="44">
+        <v>4776926305.7263327</v>
+      </c>
+      <c r="U30" s="39">
         <f t="shared" si="8"/>
-        <v>179644324.93966269</v>
-      </c>
-      <c r="V30" s="44">
+        <v>4987878516.5545425</v>
+      </c>
+      <c r="V30" s="39">
         <f t="shared" si="8"/>
-        <v>190512108.69267958</v>
-      </c>
-      <c r="W30" s="44">
+        <v>5192502161.0579062</v>
+      </c>
+      <c r="W30" s="39">
         <f t="shared" si="8"/>
-        <v>200836503.25804555</v>
-      </c>
-      <c r="X30" s="44">
+        <v>5390987096.2261696</v>
+      </c>
+      <c r="X30" s="39">
         <f t="shared" si="8"/>
-        <v>210644678.0951432</v>
-      </c>
-      <c r="Y30" s="44">
+        <v>5583517483.3393841</v>
+      </c>
+      <c r="Y30" s="39">
         <f t="shared" si="8"/>
-        <v>219962444.19038606</v>
-      </c>
-      <c r="Z30" s="44">
+        <v>5770271958.8392029</v>
+      </c>
+      <c r="Z30" s="39">
         <f t="shared" si="8"/>
-        <v>228814321.98086679</v>
-      </c>
-      <c r="AA30" s="45">
+        <v>5951423800.0740261</v>
+      </c>
+      <c r="AA30" s="40">
         <f t="shared" si="3"/>
-        <v>1779527882.3635268</v>
+        <v>79403297130.939728</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="33">
         <f>C30-$C$15</f>
-        <v>-170200000</v>
-      </c>
-      <c r="D32" s="38">
+        <v>-3000000</v>
+      </c>
+      <c r="D32" s="33">
         <f t="shared" ref="D32:Z32" si="9">D30</f>
-        <v>-122840000</v>
-      </c>
-      <c r="E32" s="38">
+        <v>361050000</v>
+      </c>
+      <c r="E32" s="33">
         <f t="shared" si="9"/>
-        <v>-96848000</v>
-      </c>
-      <c r="F32" s="38">
+        <v>704478500</v>
+      </c>
+      <c r="F32" s="33">
         <f t="shared" si="9"/>
-        <v>-72155600</v>
-      </c>
-      <c r="G32" s="38">
+        <v>1037604144.9999998</v>
+      </c>
+      <c r="G32" s="33">
         <f t="shared" si="9"/>
-        <v>-48697820</v>
-      </c>
-      <c r="H32" s="38">
+        <v>1360736020.6499996</v>
+      </c>
+      <c r="H32" s="33">
         <f t="shared" si="9"/>
-        <v>-26412929.00000003</v>
-      </c>
-      <c r="I32" s="38">
+        <v>1674173940.0304995</v>
+      </c>
+      <c r="I32" s="33">
         <f t="shared" si="9"/>
-        <v>-5242282.5500000417</v>
-      </c>
-      <c r="J32" s="38">
+        <v>1978208721.8295846</v>
+      </c>
+      <c r="J32" s="33">
         <f t="shared" si="9"/>
-        <v>14869831.577499956</v>
-      </c>
-      <c r="K32" s="38">
+        <v>2273122460.1746974</v>
+      </c>
+      <c r="K32" s="33">
         <f t="shared" si="9"/>
-        <v>33976339.998624951</v>
-      </c>
-      <c r="L32" s="38">
+        <v>2559188786.3694563</v>
+      </c>
+      <c r="L32" s="33">
         <f t="shared" si="9"/>
-        <v>52127522.998693734</v>
-      </c>
-      <c r="M32" s="38">
+        <v>2836673122.7783723</v>
+      </c>
+      <c r="M32" s="33">
         <f t="shared" si="9"/>
-        <v>69371146.848759025</v>
-      </c>
-      <c r="N32" s="38">
+        <v>3105832929.0950208</v>
+      </c>
+      <c r="N32" s="33">
         <f t="shared" si="9"/>
-        <v>85752589.506321013</v>
-      </c>
-      <c r="O32" s="38">
+        <v>3366917941.2221699</v>
+      </c>
+      <c r="O32" s="33">
         <f t="shared" si="9"/>
-        <v>101314960.03100502</v>
-      </c>
-      <c r="P32" s="38">
+        <v>3620170402.9855051</v>
+      </c>
+      <c r="P32" s="33">
         <f t="shared" si="9"/>
-        <v>116099212.02945471</v>
-      </c>
-      <c r="Q32" s="38">
+        <v>3865825290.8959398</v>
+      </c>
+      <c r="Q32" s="33">
         <f t="shared" si="9"/>
-        <v>130144251.42798197</v>
-      </c>
-      <c r="R32" s="38">
+        <v>4104110532.1690617</v>
+      </c>
+      <c r="R32" s="33">
         <f t="shared" si="9"/>
-        <v>143487038.85658288</v>
-      </c>
-      <c r="S32" s="38">
+        <v>4335247216.203989</v>
+      </c>
+      <c r="S32" s="33">
         <f t="shared" si="9"/>
-        <v>156162686.91375375</v>
-      </c>
-      <c r="T32" s="38">
+        <v>4559449799.7178688</v>
+      </c>
+      <c r="T32" s="33">
         <f t="shared" si="9"/>
-        <v>168204552.568066</v>
-      </c>
-      <c r="U32" s="38">
+        <v>4776926305.7263327</v>
+      </c>
+      <c r="U32" s="33">
         <f t="shared" si="9"/>
-        <v>179644324.93966269</v>
-      </c>
-      <c r="V32" s="38">
+        <v>4987878516.5545425</v>
+      </c>
+      <c r="V32" s="33">
         <f t="shared" si="9"/>
-        <v>190512108.69267958</v>
-      </c>
-      <c r="W32" s="38">
+        <v>5192502161.0579062</v>
+      </c>
+      <c r="W32" s="33">
         <f t="shared" si="9"/>
-        <v>200836503.25804555</v>
-      </c>
-      <c r="X32" s="38">
+        <v>5390987096.2261696</v>
+      </c>
+      <c r="X32" s="33">
         <f t="shared" si="9"/>
-        <v>210644678.0951432</v>
-      </c>
-      <c r="Y32" s="38">
+        <v>5583517483.3393841</v>
+      </c>
+      <c r="Y32" s="33">
         <f t="shared" si="9"/>
-        <v>219962444.19038606</v>
-      </c>
-      <c r="Z32" s="38">
+        <v>5770271958.8392029</v>
+      </c>
+      <c r="Z32" s="33">
         <f t="shared" si="9"/>
-        <v>228814321.98086679</v>
-      </c>
-      <c r="AA32" s="39">
+        <v>5951423800.0740261</v>
+      </c>
+      <c r="AA32" s="34">
         <f>SUM(C32:Z32)</f>
-        <v>1759527882.3635268</v>
+        <v>79393297130.939728</v>
       </c>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="42">
         <f>$C$16+C32</f>
-        <v>129800000</v>
-      </c>
-      <c r="D33" s="47">
+        <v>147000000</v>
+      </c>
+      <c r="D33" s="42">
         <f t="shared" ref="D33:Z33" si="10">C33+D32</f>
-        <v>6960000</v>
-      </c>
-      <c r="E33" s="47">
+        <v>508050000</v>
+      </c>
+      <c r="E33" s="42">
         <f t="shared" si="10"/>
-        <v>-89888000</v>
-      </c>
-      <c r="F33" s="47">
+        <v>1212528500</v>
+      </c>
+      <c r="F33" s="42">
         <f t="shared" si="10"/>
-        <v>-162043600</v>
-      </c>
-      <c r="G33" s="47">
+        <v>2250132645</v>
+      </c>
+      <c r="G33" s="42">
         <f t="shared" si="10"/>
-        <v>-210741420</v>
-      </c>
-      <c r="H33" s="47">
+        <v>3610868665.6499996</v>
+      </c>
+      <c r="H33" s="42">
         <f t="shared" si="10"/>
-        <v>-237154349.00000003</v>
-      </c>
-      <c r="I33" s="47">
+        <v>5285042605.6804991</v>
+      </c>
+      <c r="I33" s="42">
         <f t="shared" si="10"/>
-        <v>-242396631.55000007</v>
-      </c>
-      <c r="J33" s="47">
+        <v>7263251327.5100842</v>
+      </c>
+      <c r="J33" s="42">
         <f t="shared" si="10"/>
-        <v>-227526799.97250012</v>
-      </c>
-      <c r="K33" s="47">
+        <v>9536373787.684782</v>
+      </c>
+      <c r="K33" s="42">
         <f t="shared" si="10"/>
-        <v>-193550459.97387516</v>
-      </c>
-      <c r="L33" s="47">
+        <v>12095562574.054237</v>
+      </c>
+      <c r="L33" s="42">
         <f t="shared" si="10"/>
-        <v>-141422936.97518143</v>
-      </c>
-      <c r="M33" s="47">
+        <v>14932235696.832609</v>
+      </c>
+      <c r="M33" s="42">
         <f t="shared" si="10"/>
-        <v>-72051790.126422405</v>
-      </c>
-      <c r="N33" s="47">
+        <v>18038068625.927631</v>
+      </c>
+      <c r="N33" s="42">
         <f t="shared" si="10"/>
-        <v>13700799.379898608</v>
-      </c>
-      <c r="O33" s="47">
+        <v>21404986567.149803</v>
+      </c>
+      <c r="O33" s="42">
         <f t="shared" si="10"/>
-        <v>115015759.41090363</v>
-      </c>
-      <c r="P33" s="47">
+        <v>25025156970.135307</v>
+      </c>
+      <c r="P33" s="42">
         <f t="shared" si="10"/>
-        <v>231114971.44035834</v>
-      </c>
-      <c r="Q33" s="47">
+        <v>28890982261.031246</v>
+      </c>
+      <c r="Q33" s="42">
         <f t="shared" si="10"/>
-        <v>361259222.86834031</v>
-      </c>
-      <c r="R33" s="47">
+        <v>32995092793.20031</v>
+      </c>
+      <c r="R33" s="42">
         <f t="shared" si="10"/>
-        <v>504746261.72492319</v>
-      </c>
-      <c r="S33" s="47">
+        <v>37330340009.404297</v>
+      </c>
+      <c r="S33" s="42">
         <f t="shared" si="10"/>
-        <v>660908948.63867688</v>
-      </c>
-      <c r="T33" s="47">
+        <v>41889789809.122162</v>
+      </c>
+      <c r="T33" s="42">
         <f t="shared" si="10"/>
-        <v>829113501.20674288</v>
-      </c>
-      <c r="U33" s="47">
+        <v>46666716114.848495</v>
+      </c>
+      <c r="U33" s="42">
         <f t="shared" si="10"/>
-        <v>1008757826.1464056</v>
-      </c>
-      <c r="V33" s="47">
+        <v>51654594631.403038</v>
+      </c>
+      <c r="V33" s="42">
         <f t="shared" si="10"/>
-        <v>1199269934.8390851</v>
-      </c>
-      <c r="W33" s="47">
+        <v>56847096792.460945</v>
+      </c>
+      <c r="W33" s="42">
         <f t="shared" si="10"/>
-        <v>1400106438.0971308</v>
-      </c>
-      <c r="X33" s="47">
+        <v>62238083888.687119</v>
+      </c>
+      <c r="X33" s="42">
         <f t="shared" si="10"/>
-        <v>1610751116.1922741</v>
-      </c>
-      <c r="Y33" s="47">
+        <v>67821601372.026505</v>
+      </c>
+      <c r="Y33" s="42">
         <f t="shared" si="10"/>
-        <v>1830713560.3826602</v>
-      </c>
-      <c r="Z33" s="47">
+        <v>73591873330.865707</v>
+      </c>
+      <c r="Z33" s="42">
         <f t="shared" si="10"/>
-        <v>2059527882.3635268</v>
+        <v>79543297130.939728</v>
       </c>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="48">
+      <c r="C37" s="43">
         <f>(NPV($C$17,D32:Z32)+C32)/1000000</f>
-        <v>1242.9603882654465</v>
-      </c>
-      <c r="D37" s="30" t="str">
+        <v>63523.747135271406</v>
+      </c>
+      <c r="D37" s="25" t="str">
         <f>"(target: &gt; 0)"</f>
         <v>(target: &gt; 0)</v>
       </c>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="44">
         <f>IFERROR((1+IRR(C32:Z32))^12-1,0)</f>
-        <v>2.1939683923700146</v>
-      </c>
-      <c r="D38" s="30" t="str">
+        <v>1.119033503015531E+25</v>
+      </c>
+      <c r="D38" s="25" t="str">
         <f>"(target: &gt; "&amp;TEXT(CHOOSE($C$6,'1. Assumptions'!C35,'1. Assumptions'!D35,'1. Assumptions'!E35),"0.0%")&amp;")"</f>
         <v>(target: &gt; 20.0%)</v>
       </c>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="50">
+      <c r="C39" s="45">
         <f>IFERROR(MATCH(TRUE(),INDEX(C41:Z41&gt;=0,0),0),"&gt; 24")</f>
-        <v>15</v>
-      </c>
-      <c r="D39" s="30" t="str">
+        <v>2</v>
+      </c>
+      <c r="D39" s="25" t="str">
         <f>"(target: &lt; 24)"</f>
         <v>(target: &lt; 24)</v>
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="50">
+      <c r="C40" s="45" t="str">
         <f>IFERROR(MATCH(TRUE(),INDEX(C33:Z33&lt;0,0),0)-1,"&gt;= 24")</f>
-        <v>2</v>
-      </c>
-      <c r="D40" s="30" t="str">
+        <v>&gt;= 24</v>
+      </c>
+      <c r="D40" s="25" t="str">
         <f>"(target: &gt;= 12)"</f>
         <v>(target: &gt;= 12)</v>
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="52">
+      <c r="C41" s="47">
         <f>C32</f>
-        <v>-170200000</v>
-      </c>
-      <c r="D41" s="52">
+        <v>-3000000</v>
+      </c>
+      <c r="D41" s="47">
         <f t="shared" ref="D41:Z41" si="11">C41+D32</f>
-        <v>-293040000</v>
-      </c>
-      <c r="E41" s="52">
+        <v>358050000</v>
+      </c>
+      <c r="E41" s="47">
         <f t="shared" si="11"/>
-        <v>-389888000</v>
-      </c>
-      <c r="F41" s="52">
+        <v>1062528500</v>
+      </c>
+      <c r="F41" s="47">
         <f t="shared" si="11"/>
-        <v>-462043600</v>
-      </c>
-      <c r="G41" s="52">
+        <v>2100132644.9999998</v>
+      </c>
+      <c r="G41" s="47">
         <f t="shared" si="11"/>
-        <v>-510741420</v>
-      </c>
-      <c r="H41" s="52">
+        <v>3460868665.6499996</v>
+      </c>
+      <c r="H41" s="47">
         <f t="shared" si="11"/>
-        <v>-537154349</v>
-      </c>
-      <c r="I41" s="52">
+        <v>5135042605.6804991</v>
+      </c>
+      <c r="I41" s="47">
         <f t="shared" si="11"/>
-        <v>-542396631.55000007</v>
-      </c>
-      <c r="J41" s="52">
+        <v>7113251327.5100842</v>
+      </c>
+      <c r="J41" s="47">
         <f t="shared" si="11"/>
-        <v>-527526799.97250009</v>
-      </c>
-      <c r="K41" s="52">
+        <v>9386373787.684782</v>
+      </c>
+      <c r="K41" s="47">
         <f t="shared" si="11"/>
-        <v>-493550459.97387516</v>
-      </c>
-      <c r="L41" s="52">
+        <v>11945562574.054237</v>
+      </c>
+      <c r="L41" s="47">
         <f t="shared" si="11"/>
-        <v>-441422936.97518146</v>
-      </c>
-      <c r="M41" s="52">
+        <v>14782235696.832609</v>
+      </c>
+      <c r="M41" s="47">
         <f t="shared" si="11"/>
-        <v>-372051790.12642241</v>
-      </c>
-      <c r="N41" s="52">
+        <v>17888068625.927631</v>
+      </c>
+      <c r="N41" s="47">
         <f t="shared" si="11"/>
-        <v>-286299200.62010139</v>
-      </c>
-      <c r="O41" s="52">
+        <v>21254986567.149803</v>
+      </c>
+      <c r="O41" s="47">
         <f t="shared" si="11"/>
-        <v>-184984240.58909637</v>
-      </c>
-      <c r="P41" s="52">
+        <v>24875156970.135307</v>
+      </c>
+      <c r="P41" s="47">
         <f t="shared" si="11"/>
-        <v>-68885028.559641659</v>
-      </c>
-      <c r="Q41" s="52">
+        <v>28740982261.031246</v>
+      </c>
+      <c r="Q41" s="47">
         <f t="shared" si="11"/>
-        <v>61259222.868340313</v>
-      </c>
-      <c r="R41" s="52">
+        <v>32845092793.20031</v>
+      </c>
+      <c r="R41" s="47">
         <f t="shared" si="11"/>
-        <v>204746261.72492319</v>
-      </c>
-      <c r="S41" s="52">
+        <v>37180340009.404297</v>
+      </c>
+      <c r="S41" s="47">
         <f t="shared" si="11"/>
-        <v>360908948.63867694</v>
-      </c>
-      <c r="T41" s="52">
+        <v>41739789809.122162</v>
+      </c>
+      <c r="T41" s="47">
         <f t="shared" si="11"/>
-        <v>529113501.20674294</v>
-      </c>
-      <c r="U41" s="52">
+        <v>46516716114.848495</v>
+      </c>
+      <c r="U41" s="47">
         <f t="shared" si="11"/>
-        <v>708757826.1464057</v>
-      </c>
-      <c r="V41" s="52">
+        <v>51504594631.403038</v>
+      </c>
+      <c r="V41" s="47">
         <f t="shared" si="11"/>
-        <v>899269934.83908534</v>
-      </c>
-      <c r="W41" s="52">
+        <v>56697096792.460945</v>
+      </c>
+      <c r="W41" s="47">
         <f t="shared" si="11"/>
-        <v>1100106438.0971308</v>
-      </c>
-      <c r="X41" s="52">
+        <v>62088083888.687119</v>
+      </c>
+      <c r="X41" s="47">
         <f t="shared" si="11"/>
-        <v>1310751116.1922741</v>
-      </c>
-      <c r="Y41" s="52">
+        <v>67671601372.026505</v>
+      </c>
+      <c r="Y41" s="47">
         <f t="shared" si="11"/>
-        <v>1530713560.3826602</v>
-      </c>
-      <c r="Z41" s="52">
+        <v>73441873330.865707</v>
+      </c>
+      <c r="Z41" s="47">
         <f t="shared" si="11"/>
-        <v>1759527882.3635268</v>
+        <v>79393297130.939728</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
     </row>
     <row r="44" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="1" t="str">
+      <c r="C44" s="48" t="str">
         <f>IF(AND(C37&gt;0,C38&gt;CHOOSE($C$6,'1. Assumptions'!C35,'1. Assumptions'!D35,'1. Assumptions'!E35)),"✓ GO — NPV+ và IRR &gt; WACC",IF(C37&lt;0,"✗ NO-GO — NPV âm: dự án không tạo giá trị","⚠ HOLD — IRR thấp hơn kỳ vọng, cần điều chỉnh"))</f>
         <v>✓ GO — NPV+ và IRR &gt; WACC</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="6">
